--- a/bench/data/files/synthetic4_C.xlsx
+++ b/bench/data/files/synthetic4_C.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -574,17 +574,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Atlas Holdings</t>
+          <t>Xenith Bio</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -594,35 +594,35 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2011-12-21</t>
+          <t>2010-08-21</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2015-12-25</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1362.5</v>
+        <v>1475.1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3491.3</v>
+        <v>4985.6</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>348</v>
+        <v>182.7</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>627.9</v>
+        <v>287</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>926.2</v>
+        <v>722.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.312</v>
+        <v>0.849</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Robert Lopez; Matthew Brown</t>
+          <t>Thomas O'Brien; Daniel Patel; Amanda Williams; Daniel Vega; Hannah Tanaka</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -634,17 +634,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Indigo Holdings</t>
+          <t>Orion Industries</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -654,35 +654,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010-03-09</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2015-12-18</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1749.9</v>
+        <v>1821.3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5849</v>
+        <v>3423.9</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>435.2</v>
+        <v>505.9</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>376.7</v>
+        <v>565.2</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1920.6</v>
+        <v>1178.7</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.864</v>
+        <v>0.776</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Emma Nakamura; Olivia Zhang</t>
+          <t>Thomas Zhang; Wei Qureshi; Amanda Zhang; Elena Kim</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -694,17 +694,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Junction Pharma</t>
+          <t>Wavelength Energy</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -714,35 +714,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010-04-27</t>
+          <t>2010-10-13</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2015-04-17</t>
+          <t>2017-11-25</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1732</v>
+        <v>271.2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2409.4</v>
+        <v>825.4</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>344.2</v>
+        <v>71</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>586.4</v>
+        <v>73.7</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>918.7</v>
+        <v>204.3</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.721</v>
+        <v>0.795</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Sarah Qureshi; Christopher O'Brien; Andrew Patel; Andrew Hassan</t>
+          <t>Mark Zhang; Hannah Mueller</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Radial Pharma</t>
+          <t>Wavelength Group</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -774,35 +774,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2013-06-17</t>
+          <t>2013-02-20</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>264.2</v>
+        <v>869</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>622.8</v>
+        <v>1108</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>36.5</v>
+        <v>160.7</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>214</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>143.3</v>
+        <v>511.4</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.285</v>
+        <v>0.192</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Laura Yamamoto; Jennifer Xu; Olivia Johnson</t>
+          <t>Emma Ueno; Ahmed Kim; Robert Evans</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -814,17 +814,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Nova Solutions</t>
+          <t>Halo Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -834,35 +834,35 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2013-06-19</t>
+          <t>2012-01-10</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2020-03-27</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>609.7</v>
+        <v>675.9</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>599.6</v>
+        <v>730.7</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>102.4</v>
+        <v>188.1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>148.1</v>
+        <v>330.6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>456.7</v>
+        <v>588.7</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.327</v>
+        <v>0.675</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Jessica Schmidt; James Nakamura</t>
+          <t>Rachel Davis; Amanda Brown; James Xu</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -874,17 +874,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Logistics</t>
+          <t>Junction Capital</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -894,35 +894,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2012-03-14</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2019-06-03</t>
+          <t>2019-01-06</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>704.9</v>
+        <v>1903.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1328</v>
+        <v>4405.4</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>119</v>
+        <v>176.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>100.2</v>
+        <v>295</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>282.7</v>
+        <v>384.6</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.186</v>
+        <v>0.754</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Robert Johnson; Sarah Brown; Priya Ueno; Daniel Ivanov; Wei Lopez</t>
+          <t>Thomas Ueno; Thomas Tanaka; Thomas Yamamoto; James Vega</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -934,17 +934,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Apex Materials</t>
+          <t>Glacier Partners</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -954,35 +954,35 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2013-02-06</t>
+          <t>2012-09-25</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2017-03-31</t>
+          <t>2016-08-29</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1379.6</v>
+        <v>964.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1175.5</v>
+        <v>3236.4</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>374.6</v>
+        <v>245.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>562.6</v>
+        <v>315.9</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1296</v>
+        <v>409.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.987</v>
+        <v>0.795</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Elena Fischer; Michael Patel; James Zhang</t>
+          <t>Sarah Brown; Christopher Gupta; Amanda Davis</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -994,17 +994,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Meridian Inc</t>
+          <t>Delta Industries</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1014,35 +1014,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
+          <t>2011-10-22</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2017-09-04</t>
+          <t>2016-11-17</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>440</v>
+        <v>1824.6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>702.8</v>
+        <v>4430.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>293.6</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>170.8</v>
+        <v>410.8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>650.4</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.848</v>
+        <v>0.613</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Yuki Johnson; Emma Mueller</t>
+          <t>Michael Xu; Hannah Qureshi; Jessica Vega; Matthew Chen; Rachel Chen</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1052,31 +1052,129 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Fund I Average</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1030.3</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>2022.3</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>230.7</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>330.9</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>752</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Forge Partners</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2011-04-08</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2018-06-04</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1263.8</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>James Davis; Yuki Zhang; Michael Anderson; Elena Xu</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Fund I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Tessera Energy</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2013-06-07</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>2018-03-21</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1996.1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>3663.5</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>617.6</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Hannah Johnson; Priya Davis</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Fund I</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Meridian Labs</t>
+          <t>Stratus Pharma</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1086,7 +1184,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1096,215 +1194,113 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2012-10-08</t>
+          <t>2010-08-24</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2016-11-25</t>
+          <t>2013-06-05</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1023.5</v>
+        <v>76.7</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1636</v>
+        <v>178.1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>176.6</v>
+        <v>15.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>173.5</v>
+        <v>18.2</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>485.8</v>
+        <v>36.6</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.319</v>
+        <v>0.897</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Yuki Brown; Elena Mueller; Yuki Rossi; Olivia Davis</t>
+          <t>David Lopez; Thomas Patel; Yuki Nakamura; Jessica Williams; Olivia Nakamura</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund I</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Beacon Systems</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2012-07-21</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>2020-05-27</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1181.7</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2928.2</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>268.5</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>301.7</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>651.4</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>Thomas Williams; Priya Qureshi</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>Fund II</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Indigo Systems</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Munich, DE</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2014-10-18</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2020-11-22</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1229.1</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1883.8</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>471.2</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>319.1</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Christopher Rossi; Emma Mueller; Elena Qureshi</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>Fund II</t>
-        </is>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Fund I Average</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1113.6</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2568.3</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>494.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Drift Bio</t>
+          <t>Junction Networks</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2014-05-06</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
+          <t>2013-04-02</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
-        <v>460.9</v>
+        <v>689.9</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>581.8</v>
+        <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>43.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>93</v>
+        <v/>
       </c>
       <c r="K18" s="4" t="n">
-        <v>29.3</v>
+        <v>310</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.791</v>
+        <v>0.836</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>James Ueno; Sarah Ueno; Elena Nakamura</t>
+          <t>Michael Davis; Wei Fischer; Mark Lopez; Amanda Mueller; Ravi Tanaka</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1316,51 +1312,55 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Stratus Labs</t>
+          <t>Iris AG</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2015-01-26</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>2013-01-08</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>2019-12-24</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
-        <v>1878.5</v>
+        <v>967.3</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v/>
+        <v>761.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>216.2</v>
+        <v>142.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v/>
+        <v>167.6</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>444.5</v>
+        <v>449.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.292</v>
+        <v>0.775</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Olivia Evans; David Gupta; Christopher Mueller; Emma Gupta</t>
+          <t>Ravi Williams; Laura O'Brien; Christopher Lopez; Mark Nakamura; Elena Ivanov</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1372,17 +1372,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Xenith AG</t>
+          <t>Nova SA</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1392,35 +1392,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2014-04-26</t>
+          <t>2013-07-20</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2019-04-05</t>
+          <t>2017-06-08</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>88.8</v>
+        <v>516.5</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>247.4</v>
+        <v>564.3</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>19.1</v>
+        <v>98.2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>37.4</v>
+        <v>165.4</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>77.3</v>
+        <v>162.8</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.343</v>
+        <v>0.4</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Christopher Anderson; Thomas Qureshi; Amanda Davis; Jessica Kim; Daniel Gupta</t>
+          <t>Matthew O'Brien; Priya Tanaka</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1432,51 +1432,55 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Partners</t>
+          <t>Indigo Dynamics</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2014-10-20</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>2014-01-21</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2020-02-04</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
-        <v>835.3</v>
+        <v>483.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v/>
+        <v>883.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>120.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v/>
+        <v>140.5</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.893</v>
+        <v>0.787</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Rachel Patel; Matthew Zhang; Christopher Rossi</t>
+          <t>Jennifer Kim; Elena Lopez; Priya Evans; Olivia Hassan</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1488,17 +1492,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Meridian Foods</t>
+          <t>Yields Systems</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1508,35 +1512,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2014-09-24</t>
+          <t>2013-07-24</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2017-05-20</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1342.6</v>
+        <v>1306.9</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3085.9</v>
+        <v>1961.9</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>372.7</v>
+        <v>203.1</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>397.8</v>
+        <v>342.1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>459.4</v>
+        <v>614.9</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.68</v>
+        <v>0.446</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Amanda Xu; Amanda Rossi; Hannah Anderson; Mark Ueno</t>
+          <t>Hannah Rossi; Sarah Ueno; Thomas Patel; Jessica Patel; Matthew Evans</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1548,17 +1552,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Apex Health</t>
+          <t>Orion Foods</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1568,35 +1572,35 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2015-06-01</t>
+          <t>2013-10-09</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2021-07-03</t>
+          <t>2017-12-16</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1557</v>
+        <v>1651.5</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3506.2</v>
+        <v>4722.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>147.9</v>
+        <v>156.9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>355.9</v>
+        <v>178.7</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>389.8</v>
+        <v>284.6</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.404</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Thomas Brown; Rachel Brown; Priya Patel; James Nakamura</t>
+          <t>Matthew Mueller; David Qureshi; Jessica Chen; Elena Gupta</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1608,17 +1612,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Junction Materials</t>
+          <t>Glacier Materials</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1628,35 +1632,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2012-10-08</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2018-12-19</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>601.2</v>
+        <v>1595</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2098.9</v>
+        <v>2512.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>165.9</v>
+        <v>356.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>358.8</v>
+        <v>302</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>468.1</v>
+        <v>1219.6</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.869</v>
+        <v>0.928</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Michael Fischer; Hannah Fischer; Amanda Schmidt; David Patel</t>
+          <t>Priya Rossi; Daniel Davis</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -1668,17 +1672,17 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Fathom Dynamics</t>
+          <t>Iris Foods</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1688,35 +1692,35 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-05-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2019-04-25</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1599.9</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1586.1</v>
+        <v>212.2</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>241.6</v>
+        <v>22.7</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>198.3</v>
+        <v>35.8</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>830.6</v>
+        <v>25</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.679</v>
+        <v>0.415</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Ravi Lopez; Yuki Brown; Christopher Hassan; Thomas Yamamoto</t>
+          <t>Priya Brown; Rachel O'Brien; Olivia Zhang</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -1728,17 +1732,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Nova Corp</t>
+          <t>Indigo Health</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1748,35 +1752,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2012-01-07</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2020-03-20</t>
+          <t>2016-11-22</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>409.3</v>
+        <v>1524.6</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>698.7</v>
+        <v>1344.3</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>94.5</v>
+        <v>237.8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>186.8</v>
+        <v>210.1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>402</v>
+        <v>603.4</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.754</v>
+        <v>0.843</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Xu; Michael Fischer; Matthew Chen; Wei Anderson; Priya Vega</t>
+          <t>Michael Tanaka; Hannah Fischer; Wei Yamamoto</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -1788,17 +1792,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Echo Foods</t>
+          <t>Nova Capital</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1808,35 +1812,35 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2013-12-10</t>
+          <t>2014-02-15</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2018-12-13</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>798.3</v>
+        <v>1587</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1831.4</v>
+        <v>1530.2</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>194.1</v>
+        <v>421.7</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>266.1</v>
+        <v>748.5</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>211.6</v>
+        <v>1696.2</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.791</v>
+        <v>0.217</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Amanda Zhang; Andrew Williams; Jessica Johnson; Andrew Hassan; Ahmed Fischer</t>
+          <t>Laura Davis; Andrew Ueno; Laura Ivanov; Wei Rossi</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -1846,36 +1850,134 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Fund II Average</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>1000.5</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1825.9</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>258.2</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>372.1</v>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ember Logistics</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2012-01-28</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2016-03-12</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1246.6</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1299.2</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>781.1</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Yuki Williams; Laura Chen</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Fund II</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Radial AG</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2015-12-02</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2018-10-24</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>898.4</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1060.8</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Mueller; Sarah Ivanov; Emma Kim</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Fund II</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Echo Health</t>
+          <t>Nova Materials</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1890,57 +1992,57 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2015-01-17</t>
+          <t>2012-03-26</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2018-11-21</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>482.6</v>
+        <v>821.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1151.5</v>
+        <v>2719.1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>56.7</v>
+        <v>188.5</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>113.5</v>
+        <v>290.8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>119.5</v>
+        <v>408.9</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>James Kim; James Zhang; Amanda O'Brien; Sophie Schmidt</t>
+          <t>Matthew Tanaka; Andrew Brown; Emma Kim; Jessica Schmidt</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Tessera Systems</t>
+          <t>Tessera Pharma</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1950,57 +2052,57 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2016-06-27</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-05-22</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>975.3</v>
+        <v>663</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2835.6</v>
+        <v>768.7</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>234.5</v>
+        <v>104.1</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>355.9</v>
+        <v>133</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>173.1</v>
+        <v>275.7</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.437</v>
+        <v>0.594</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Robert O'Brien; David Patel</t>
+          <t>Mark Patel; Priya Patel; James Lopez</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Atlas Media</t>
+          <t>Junction GmbH</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2010,57 +2112,57 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2016-05-27</t>
+          <t>2014-06-13</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>175.7</v>
+        <v>270.7</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>153.9</v>
+        <v>909.1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>17.4</v>
+        <v>49.3</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>43.1</v>
+        <v>101.4</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>73.09999999999999</v>
+        <v>196.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.925</v>
+        <v>0.626</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>James Schmidt; Sarah Kim; Priya Qureshi</t>
+          <t>Sophie Schmidt; Emma Gupta; David Xu; Laura Anderson; Wei Gupta</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Nimbus SA</t>
+          <t>Tessera Tech</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2070,57 +2172,57 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
+          <t>2015-07-05</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2018-05-19</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1563.5</v>
+        <v>1875.6</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3006.7</v>
+        <v>3801.9</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>324.5</v>
+        <v>477.9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>670.1</v>
+        <v>805</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>315.1</v>
+        <v>1392.1</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.715</v>
+        <v>0.726</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Priya Schmidt; Thomas Fischer</t>
+          <t>Sophie Hassan; Jessica Tanaka; Olivia Anderson; Ahmed Kim</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Orion Materials</t>
+          <t>Bloom Logistics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2130,173 +2232,79 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2015-01-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2017-11-05</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1341.9</v>
+        <v>1652.7</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3000.4</v>
+        <v>5204.8</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>336.7</v>
+        <v>269.5</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>529.4</v>
+        <v>663.2</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>350.2</v>
+        <v>1110.1</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.42</v>
+        <v>0.212</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Ravi Qureshi; Matthew Xu; Priya Mueller</t>
+          <t>Thomas Nakamura; Michael Kim</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Forge Dynamics</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>2016-06-12</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>1326.9</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>3540</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>398.2</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>437.1</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Andrew Zhang; Matthew Rossi; Hannah Rossi; Jennifer Rossi</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Lumen Dynamics</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Tokyo, JP</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>James Vega; Thomas Chen</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Fund II Average</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>1049.2</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1891.1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>192.1</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>572.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Iris Media</t>
+          <t>Iris Solutions</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2306,35 +2314,35 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2016-03-10</t>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2020-04-11</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>623.6</v>
+        <v>307.5</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1295.6</v>
+        <v>282.8</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>147.4</v>
+        <v>35</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>239.1</v>
+        <v>29.7</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>219</v>
+        <v>76.8</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.213</v>
+        <v>0.631</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Olivia Rossi; Sophie Mueller; Hannah Brown; Olivia Evans; Elena Brown</t>
+          <t>Sophie Mueller; Sarah Vega; Jessica Davis; Ravi Johnson</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2346,17 +2354,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Vertex Systems</t>
+          <t>Junction Industries</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2366,35 +2374,35 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2015-12-17</t>
+          <t>2014-01-14</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2018-12-09</t>
+          <t>2020-02-10</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>348.4</v>
+        <v>1964.6</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1025.8</v>
+        <v>6381.6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>96.8</v>
+        <v>299.1</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>139.5</v>
+        <v>392.4</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>150.5</v>
+        <v>681.6</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Priya Ivanov; Sophie O'Brien; Robert Gupta; James Williams</t>
+          <t>Elena Anderson; Amanda Davis; Jessica Hassan</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -2406,17 +2414,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Foods</t>
+          <t>Helix Logistics</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2426,35 +2434,35 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
+          <t>2017-05-21</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1265.2</v>
+        <v>1329.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>4092.9</v>
+        <v>4392.4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>305</v>
+        <v>123.8</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>727.1</v>
+        <v>200.2</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>966</v>
+        <v>552.2</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.206</v>
+        <v>0.535</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Olivia Gupta; Sarah Tanaka; Emma Qureshi</t>
+          <t>Sophie Davis; Amanda Patel; Daniel Ueno; Yuki Evans</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -2466,51 +2474,55 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Forge GmbH</t>
+          <t>Yields Industries</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2015-08-28</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+          <t>2016-12-21</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
-        <v>1974.5</v>
+        <v>382.5</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v/>
+        <v>328.7</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>499.6</v>
+        <v>49.1</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v/>
+        <v>91.7</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>284.9</v>
+        <v>106.7</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.314</v>
+        <v>0.632</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Laura Xu; Olivia Patel; Jennifer Zhang</t>
+          <t>Elena Lopez; Wei Anderson; Robert Rossi; Sophie Hassan</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2522,17 +2534,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Umbra Bio</t>
+          <t>Quanta Pharma</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2542,35 +2554,35 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-03-08</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>494.8</v>
+        <v>958.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1478</v>
+        <v>1301.4</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>97.8</v>
+        <v>132.6</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>177.4</v>
+        <v>199.6</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>307.4</v>
+        <v>124.5</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.54</v>
+        <v>0.622</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Michael Kim; Wei Qureshi; Elena Mueller; Matthew Evans</t>
+          <t>Jessica Zhang; Christopher Fischer; Michael Yamamoto</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2582,17 +2594,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Group</t>
+          <t>Apex Logic</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2602,35 +2614,35 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2014-01-22</t>
+          <t>2015-01-27</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2022-03-14</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1186.9</v>
+        <v>843.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3530.2</v>
+        <v>2201</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>108.7</v>
+        <v>157.8</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>183.7</v>
+        <v>288</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>70.5</v>
+        <v>597.8</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.862</v>
+        <v>0.626</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Laura Vega; Yuki Mueller; Hannah Hassan</t>
+          <t>Ahmed Williams; Robert Evans; Rachel Patel</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -2642,55 +2654,51 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Zenith Foods</t>
+          <t>Iris Inc</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
+          <t>2014-02-05</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
-        <v>1409.6</v>
+        <v>1359.3</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>4169.9</v>
+        <v/>
       </c>
       <c r="I43" s="4" t="n">
-        <v>227.9</v>
+        <v>180.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>301.3</v>
+        <v/>
       </c>
       <c r="K43" s="4" t="n">
-        <v>708.1</v>
+        <v>94.8</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.638</v>
+        <v>0.973</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Sophie Schmidt; James Williams; Rachel Qureshi; Laura Mueller; Sophie Ivanov</t>
+          <t>Yuki Ivanov; Jessica Kim; Ravi O'Brien; Jennifer Rossi; David Qureshi</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -2702,12 +2710,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Ember Labs</t>
+          <t>Gravity Materials</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2722,35 +2730,35 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2016-03-18</t>
+          <t>2017-05-07</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1247.4</v>
+        <v>1683.1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>3068.9</v>
+        <v>1822.7</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>252.1</v>
+        <v>228.3</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>509.4</v>
+        <v>332.5</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>233.4</v>
+        <v>690.5</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.837</v>
+        <v>0.632</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Yuki Xu; Christopher Hassan</t>
+          <t>Laura Mueller; James Zhang</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -2762,17 +2770,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Materials</t>
+          <t>Tessera Group</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2782,35 +2790,35 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2014-11-04</t>
+          <t>2017-01-05</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2019-01-29</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>348.3</v>
+        <v>1735</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>567.3</v>
+        <v>1359.2</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>97</v>
+        <v>478.1</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>111</v>
+        <v>798.1</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>59.7</v>
+        <v>1951</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.71</v>
+        <v>0.178</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Wei Anderson; Olivia Tanaka; Robert Evans</t>
+          <t>Amanda Patel; Sarah Patel; Daniel Evans; Christopher Gupta; Elena Lopez</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -2822,51 +2830,55 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Atlas Energy</t>
+          <t>Apex Media</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2017-02-18</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>2014-11-08</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
-        <v>859.6</v>
+        <v>302.7</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v/>
+        <v>1023.2</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>78.40000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v/>
+        <v>115</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>240.3</v>
+        <v>41.7</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.665</v>
+        <v>0.491</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Mark Mueller; Matthew Kim</t>
+          <t>Michael Yamamoto; Thomas Zhang; Mark Schmidt; Jennifer Anderson</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -2878,55 +2890,51 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Indigo Materials</t>
+          <t>Junction Foods</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2016-08-02</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
+          <t>2017-12-25</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
-        <v>1821.9</v>
+        <v>413.5</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3990.8</v>
+        <v/>
       </c>
       <c r="I47" s="4" t="n">
-        <v>290.6</v>
+        <v>51.4</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>665.9</v>
+        <v/>
       </c>
       <c r="K47" s="4" t="n">
-        <v>755.3</v>
+        <v>175.8</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.89</v>
+        <v>0.586</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Sarah O'Brien; Amanda Evans; Mark Gupta; Matthew Lopez; Rachel Yamamoto</t>
+          <t>Olivia Schmidt; Amanda Yamamoto</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -2938,219 +2946,219 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Glacier Energy</t>
+          <t>Radial Group</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2015-02-21</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>2018-04-09</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>1837.3</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>6251.3</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>387</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>691.7</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Johnson; Rachel Brown</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Fund III</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Fund III Average</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>1093</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>2534.4</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>482.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Delta Networks</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>2017-11-13</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>2020-09-12</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>715.7</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>1416.7</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>203.7</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>450.3</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
-        <is>
-          <t>Mark Nakamura; James Williams</t>
-        </is>
-      </c>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Junction Capital</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>2014-06-20</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>2020-04-24</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>471.7</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>1635.3</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>139.5</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
-        <is>
-          <t>Ravi Fischer; Daniel Brown; James Anderson; Elena Davis</t>
-        </is>
-      </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Mosaic Materials</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Paris, FR</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>2014-08-16</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>753.4</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>1088.9</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>183.2</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>275.8</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>249.5</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
-          <t>Emma O'Brien; Robert Rossi</t>
-        </is>
-      </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Fund III Average</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>931.9</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>2280.5</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>179.2</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>321.3</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>302.9</v>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Toronto, CA</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2019-04-08</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>741.2</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>1345.7</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>156.7</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Tanaka; Amanda Anderson</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Apex Tech</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>2018-04-27</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1652.9</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>5164.1</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>679.1</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>1767.3</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>Laura Brown; Laura Johnson; David Evans; Christopher Yamamoto</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Bio</t>
+          <t>Drift Systems</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3160,35 +3168,35 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2016-09-21</t>
+          <t>2016-12-24</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1810.6</v>
+        <v>1320.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>4242.6</v>
+        <v>1347.6</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>396.1</v>
+        <v>356.4</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>570.2</v>
+        <v>298.2</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1686.2</v>
+        <v>187.1</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.33</v>
+        <v>0.486</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Daniel Qureshi; Andrew Mueller; Hannah Schmidt; Amanda Schmidt; Yuki Ivanov</t>
+          <t>Olivia Anderson; Michael Chen; Rachel Hassan; Jennifer Williams; Priya Yamamoto</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -3200,17 +3208,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Radial Partners</t>
+          <t>Stratus Systems</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3220,35 +3228,35 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2016-02-26</t>
+          <t>2017-03-25</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2020-01-03</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1764.6</v>
+        <v>1914.4</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>5231</v>
+        <v>5440</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>311.2</v>
+        <v>383.2</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>290.9</v>
+        <v>500.1</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>249.6</v>
+        <v>1028</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.258</v>
+        <v>0.784</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Jessica Anderson; Sophie Johnson; Andrew Nakamura; Elena Xu; Laura Rossi</t>
+          <t>Olivia Patel; Elena O'Brien</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -3260,17 +3268,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Zenith Inc</t>
+          <t>Polaris Corp</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3280,35 +3288,35 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2016-03-18</t>
+          <t>2018-05-04</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1705.5</v>
+        <v>1410</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>4966.7</v>
+        <v>1590.4</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>354.2</v>
+        <v>290.6</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>573.2</v>
+        <v>341.8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>962.8</v>
+        <v>854.3</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.45</v>
+        <v>0.964</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Rachel Yamamoto; Matthew Ueno; Amanda Davis; Sophie Ivanov</t>
+          <t>Elena Lopez; Sophie Vega; Jessica Gupta</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -3320,17 +3328,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Nova Industries</t>
+          <t>Xenith Networks</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3340,35 +3348,35 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2017-08-04</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1761.8</v>
+        <v>838.1</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>5896.7</v>
+        <v>845.1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>399.5</v>
+        <v>195.2</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>656.8</v>
+        <v>332.5</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1305.5</v>
+        <v>846.3</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.15</v>
+        <v>0.806</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Matthew Hassan; Hannah Yamamoto; Mark Anderson; Amanda Kim; Ravi Johnson</t>
+          <t>Hannah Gupta; Jennifer Evans; Olivia Vega</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -3380,7 +3388,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Krypton Logistics</t>
+          <t>Gravity Corp</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3390,7 +3398,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3400,35 +3408,35 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2018-09-14</t>
+          <t>2018-11-18</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1562.1</v>
+        <v>683.2</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>4412.2</v>
+        <v>956.9</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>224.3</v>
+        <v>167.1</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>388.5</v>
+        <v>350.2</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>781.3</v>
+        <v>522</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.625</v>
+        <v>0.876</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Amanda Johnson; Hannah Davis; Olivia Nakamura; Olivia Qureshi; Daniel Anderson</t>
+          <t>James Rossi; Mark Evans</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -3440,17 +3448,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Beacon Tech</t>
+          <t>Xenith Materials</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3460,35 +3468,35 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>2017-07-26</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>998.9</v>
+        <v>1434.6</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2791.2</v>
+        <v>4460</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>142.2</v>
+        <v>219.4</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>204.3</v>
+        <v>499.5</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>605.3</v>
+        <v>469.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.497</v>
+        <v>0.299</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Rachel Johnson; Ahmed Xu; Elena Fischer</t>
+          <t>Wei O'Brien; Sophie Schmidt; Priya Rossi; Michael Xu</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -3500,7 +3508,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Drift Solutions</t>
+          <t>Wavelength SA</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3510,7 +3518,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3520,35 +3528,35 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2019-05-20</t>
+          <t>2016-06-04</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>1500</v>
+        <v>1119.3</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>3846</v>
+        <v>837.5</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>350.1</v>
+        <v>120.7</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>334.9</v>
+        <v>207.4</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1239.5</v>
+        <v>265</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0.464</v>
+        <v>0.625</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Sophie Anderson; Emma Fischer</t>
+          <t>Ahmed Davis; David Xu; Olivia Qureshi; Rachel Davis</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -3560,55 +3568,51 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Fathom Networks</t>
+          <t>Atlas Media</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-01</t>
-        </is>
-      </c>
+          <t>2016-10-22</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
-        <v>1198.6</v>
+        <v>244</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1903</v>
+        <v/>
       </c>
       <c r="I60" s="4" t="n">
-        <v>120.7</v>
+        <v>45</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>177.4</v>
+        <v/>
       </c>
       <c r="K60" s="4" t="n">
-        <v>492.6</v>
+        <v>122.8</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.797</v>
+        <v>0.415</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Rachel Williams; Rachel Williams</t>
+          <t>Amanda Vega; Jessica Williams; Emma Tanaka</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -3620,17 +3624,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Lumen AG</t>
+          <t>Xenith AG</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3640,35 +3644,35 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>186.5</v>
+        <v>1594.1</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>182.8</v>
+        <v>3706.9</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>26.9</v>
+        <v>427.7</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>35.6</v>
+        <v>370.9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>18.7</v>
+        <v>997.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0.392</v>
+        <v>0.487</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>David Tanaka; Elena Rossi; Elena Qureshi; Jessica Anderson</t>
+          <t>Matthew Hassan; Mark Qureshi; Matthew Tanaka</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -3680,17 +3684,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Materials</t>
+          <t>Lattice Health</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3700,35 +3704,35 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2022-01-30</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>970.9</v>
+        <v>313.5</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1829.6</v>
+        <v>864.2</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>240.8</v>
+        <v>55.2</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>376.1</v>
+        <v>66.7</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>906.5</v>
+        <v>236</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.766</v>
+        <v>0.875</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Mueller; Mark Chen; James Ivanov</t>
+          <t>Michael Anderson; Elena Patel; Wei Mueller; Elena Williams</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -3740,17 +3744,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Quanta Ltd</t>
+          <t>Kepler Bio</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3760,35 +3764,35 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2019-10-04</t>
+          <t>2019-10-14</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1087.7</v>
+        <v>1589.4</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>798.6</v>
+        <v>3917.9</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>268.7</v>
+        <v>259.1</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>348.1</v>
+        <v>438.4</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>773.6</v>
+        <v>829.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>0.17</v>
+        <v>0.293</v>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>Mark Gupta; David O'Brien</t>
+          <t>Hannah Tanaka; Robert Tanaka; Olivia Anderson; David Williams</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -3800,12 +3804,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Orion Dynamics</t>
+          <t>Apex Partners</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3820,35 +3824,35 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2019-02-19</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>803.9</v>
+        <v>1046.6</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>2180.7</v>
+        <v>884.5</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>113.4</v>
+        <v>156.6</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>128.8</v>
+        <v>243.7</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>184</v>
+        <v>481.2</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.742</v>
+        <v>0.639</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Andrew Ivanov; Laura Nakamura; David Nakamura</t>
+          <t>Rachel Vega; Jessica Mueller; Matthew Ueno; Daniel Ivanov</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -3858,41 +3862,139 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Fund IV Average</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>1279.3</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>3190.1</v>
-      </c>
-      <c r="I65" s="6" t="n">
-        <v>245.7</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>340.4</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>767.1</v>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Fathom Solutions</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>2017-09-06</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>1933.3</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>4976.1</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>690.3</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Gupta; Ravi Fischer; Rachel Williams</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Echo GmbH</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Toronto, CA</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>2017-12-24</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>1188.7</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>2995.9</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Wei Lopez; Ahmed Patel; Wei Ivanov; Olivia Chen; Michael Tanaka</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Beacon Inc</t>
+          <t>Fathom Energy</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3902,168 +4004,74 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>526</v>
+        <v>361.5</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>600.8</v>
+        <v>1051.9</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>138.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>305.3</v>
+        <v>135</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>470.4</v>
+        <v>317.8</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.864</v>
+        <v>0.161</v>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>Thomas Tanaka; Sarah Chen; Christopher Ivanov; Rachel Rossi; Andrew Lopez</t>
+          <t>Ravi Williams; Jennifer Xu; Robert Davis; Daniel Xu</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Tessera Bio</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Munich, DE</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>1492.4</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>4176.3</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>337.4</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>433.9</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>1138.1</v>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
-        <is>
-          <t>Sarah Schmidt; Matthew Zhang; Mark Mueller</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Fathom Logic</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="n">
-        <v>226.9</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="K69" s="4" t="n">
-        <v>151.9</v>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="M69" s="4" t="inlineStr">
-        <is>
-          <t>Thomas Schmidt; Christopher Chen</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
-        </is>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Fund IV Average</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>1140.3</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>2524</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>230.7</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>564.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Lumen Partners</t>
+          <t>Zenith Materials</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4073,36 +4081,40 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
+          <t>2018-05-08</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
-        <v>321.1</v>
+        <v>1640.7</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v/>
+        <v>1322.9</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>77.3</v>
+        <v>409.3</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v/>
+        <v>588.5</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>302.1</v>
+        <v>1391.4</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.377</v>
+        <v>0.871</v>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>Ravi Xu; Ravi O'Brien; Sophie Evans</t>
+          <t>Michael Ueno; Yuki Brown; Sarah Patel; Daniel Hassan</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -4114,7 +4126,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Iris Industries</t>
+          <t>Nimbus Holdings</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -4124,7 +4136,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -4134,35 +4146,35 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2019-10-13</t>
+          <t>2019-02-09</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2022-12-02</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>236.8</v>
+        <v>1951.1</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>366.8</v>
+        <v>1614.5</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>48</v>
+        <v>167.1</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>92.8</v>
+        <v>200.8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>50.2</v>
+        <v>413.5</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>0.243</v>
+        <v>0.297</v>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>Robert Anderson; Emma Williams; Ravi Mueller</t>
+          <t>Thomas Qureshi; Daniel Yamamoto; Amanda Kim; Sarah Rossi</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -4174,51 +4186,55 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Cipher Dynamics</t>
+          <t>Xenith Foods</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2020-01-14</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr"/>
+          <t>2020-10-23</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
-        <v>1078.2</v>
+        <v>1760.5</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v/>
+        <v>1848.6</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>184.4</v>
+        <v>418.7</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v/>
+        <v>706.6</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>217.4</v>
+        <v>1348.3</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.874</v>
+        <v>0.195</v>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>Michael Williams; David Yamamoto; Ahmed Mueller; Emma Anderson; Emma Qureshi</t>
+          <t>Ahmed Williams; Jennifer Kim; Ahmed Tanaka; Priya Vega; Elena Schmidt</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -4230,17 +4246,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Capital</t>
+          <t>Zenith Energy</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -4250,35 +4266,35 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2018-01-08</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1063.5</v>
+        <v>1147.3</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>948.4</v>
+        <v>2182.6</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>213.8</v>
+        <v>180.7</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>471.1</v>
+        <v>208.6</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>195.2</v>
+        <v>289.4</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>0.743</v>
+        <v>0.596</v>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Mark Kim; Thomas Chen; Jennifer Brown; Hannah Ivanov; James Nakamura</t>
+          <t>Jessica Xu; Yuki Ivanov; Sophie Brown; Hannah Evans</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -4290,17 +4306,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Fathom Media</t>
+          <t>Forge Systems</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -4310,35 +4326,35 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2020-01-20</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>489.4</v>
+        <v>1208.7</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1683.4</v>
+        <v>3926.9</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>84</v>
+        <v>199.7</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>128.7</v>
+        <v>253.5</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>244.3</v>
+        <v>864.3</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.153</v>
+        <v>0.242</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>Rachel Xu; Amanda Mueller; Yuki Vega; Christopher Davis</t>
+          <t>James Davis; Olivia Qureshi; Priya Ivanov; Jennifer Evans; Olivia Gupta</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -4350,17 +4366,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Quanta Labs</t>
+          <t>Helix SA</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -4370,35 +4386,35 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
+          <t>2019-11-08</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1086.1</v>
+        <v>126.4</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1781.9</v>
+        <v>169.3</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>212.5</v>
+        <v>14</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>412.3</v>
+        <v>19.2</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>714.4</v>
+        <v>33.8</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>0.368</v>
+        <v>0.616</v>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>Yuki Davis; James Davis; Priya Ivanov</t>
+          <t>Michael Rossi; Mark Fischer</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -4410,17 +4426,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Media</t>
+          <t>Zenith GmbH</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -4430,35 +4446,35 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>823.3</v>
+        <v>806.2</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>2065</v>
+        <v>675.9</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>195.9</v>
+        <v>148</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>465.6</v>
+        <v>357</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>330.6</v>
+        <v>379.5</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.249</v>
+        <v>0.791</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>Sophie Davis; Jessica Xu; Olivia Mueller</t>
+          <t>Jennifer Chen; Daniel Kim</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -4470,17 +4486,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Indigo Health</t>
+          <t>Gravity Group</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -4490,35 +4506,35 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>928.3</v>
+        <v>1507.3</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>1740.5</v>
+        <v>4927.5</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>87.3</v>
+        <v>167.8</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>162</v>
+        <v>199.1</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>360.9</v>
+        <v>331.3</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>0.618</v>
+        <v>0.957</v>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>Thomas Zhang; Robert Kim; James Ivanov; Ravi Brown; Jessica Zhang</t>
+          <t>Laura Chen; Sophie Patel</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -4530,17 +4546,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Partners</t>
+          <t>Beacon Materials</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4550,35 +4566,35 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>220.3</v>
+        <v>57.3</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>708</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>27.8</v>
+        <v>7.2</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>39.1</v>
+        <v>11.6</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>26.2</v>
+        <v>9.4</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.392</v>
+        <v>0.575</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>Ravi Ivanov; Robert Nakamura</t>
+          <t>Mark Rossi; Mark Qureshi; Rachel Ivanov</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -4590,17 +4606,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Echo SA</t>
+          <t>Stratus Holdings</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4610,35 +4626,35 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>1878.6</v>
+        <v>1658.1</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>6132.7</v>
+        <v>4969.7</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>410.8</v>
+        <v>152.1</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>545.3</v>
+        <v>123.9</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1266.2</v>
+        <v>160</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>0.857</v>
+        <v>0.283</v>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>Ravi Yamamoto; Christopher Brown; Michael Rossi; Sarah Schmidt</t>
+          <t>Jennifer O'Brien; Priya Hassan; Olivia Brown; Jennifer Fischer</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -4650,17 +4666,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Umbra Dynamics</t>
+          <t>Bloom Networks</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4670,35 +4686,35 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2019-10-27</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>1545.8</v>
+        <v>1376.1</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>2735.4</v>
+        <v>1165.1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>322</v>
+        <v>217.8</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>275.4</v>
+        <v>191.9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>193.8</v>
+        <v>574.1</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.643</v>
+        <v>0.481</v>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>Matthew Kim; Daniel Lopez; Thomas O'Brien; Matthew Williams</t>
+          <t>Robert Anderson; Yuki Anderson; David Ivanov; James Lopez</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -4708,135 +4724,139 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Nimbus Solutions</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Fund V Average</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>1203.6</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>2079</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>260.1</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>526.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Radial Networks</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Chicago, IL</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="n">
-        <v>209.3</v>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>294.8</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="M81" s="4" t="inlineStr">
-        <is>
-          <t>Sophie Anderson; Priya Anderson</t>
-        </is>
-      </c>
-      <c r="N81" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Fund V Average</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="n">
-        <v>808.4</v>
-      </c>
-      <c r="H82" s="6" t="n">
-        <v>1936.2</v>
-      </c>
-      <c r="I82" s="6" t="n">
-        <v>160.7</v>
-      </c>
-      <c r="J82" s="6" t="n">
-        <v>279.2</v>
-      </c>
-      <c r="K82" s="6" t="n">
-        <v>380.9</v>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>2022-02-06</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>Robert Nakamura; Yuki Yamamoto</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>Fund VI</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Lattice Systems</t>
+          <t>Echo Health</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
-        <v>1093.2</v>
+        <v>677.7</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v/>
+        <v>1817.2</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>156.5</v>
+        <v>91.2</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v/>
+        <v>164.2</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>487.4</v>
+        <v>201</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.357</v>
+        <v>0.249</v>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>Laura O'Brien; Matthew Zhang; Ravi Ivanov</t>
+          <t>Michael Ivanov; Christopher Nakamura; Amanda Mueller; Mark Rossi</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -4848,17 +4868,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Apex Industries</t>
+          <t>Umbra Energy</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4868,31 +4888,31 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
-        <v>1319.9</v>
+        <v>1297.1</v>
       </c>
       <c r="H85" s="4" t="n">
         <v/>
       </c>
       <c r="I85" s="4" t="n">
-        <v>287.9</v>
+        <v>111.6</v>
       </c>
       <c r="J85" s="4" t="n">
         <v/>
       </c>
       <c r="K85" s="4" t="n">
-        <v>862.9</v>
+        <v>292.1</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>0.405</v>
+        <v>0.197</v>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>Andrew Vega; Christopher Zhang; Daniel Vega; Jessica Johnson</t>
+          <t>Christopher Qureshi; Wei Vega</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -4904,17 +4924,17 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Apex Media</t>
+          <t>Orion Solutions</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4924,35 +4944,35 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>702.8</v>
+        <v>442.8</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1171.3</v>
+        <v>439.8</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>193.2</v>
+        <v>76.2</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>251.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>735.2</v>
+        <v>259.1</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.241</v>
+        <v>0.382</v>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>Laura Kim; Thomas Ueno</t>
+          <t>Priya Qureshi; Robert Lopez</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -4964,55 +4984,51 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Kepler Group</t>
+          <t>Junction Tech</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
-        <v>1151.4</v>
+        <v>1411.8</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1446</v>
+        <v/>
       </c>
       <c r="I87" s="4" t="n">
-        <v>101.5</v>
+        <v>229</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>188.1</v>
+        <v/>
       </c>
       <c r="K87" s="4" t="n">
-        <v>207.2</v>
+        <v>474.1</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>0.837</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>Andrew Gupta; Priya Johnson; Olivia Rossi; Elena Zhang</t>
+          <t>Christopher Rossi; Ravi Fischer</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -5024,17 +5040,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Atlas Logic</t>
+          <t>Drift Energy</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5044,35 +5060,35 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>1342.1</v>
+        <v>554</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>3202.5</v>
+        <v>1430.1</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>375.2</v>
+        <v>45</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>316.2</v>
+        <v>46.3</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1254.7</v>
+        <v>74.3</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.234</v>
+        <v>0.499</v>
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>Matthew Ueno; Elena Johnson; Rachel Chen; Robert Ivanov; Jessica Williams</t>
+          <t>Yuki Fischer; Mark Ueno; Yuki Rossi; David O'Brien</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -5084,17 +5100,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Zenith Energy</t>
+          <t>Echo Tech</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -5104,31 +5120,31 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
-        <v>1952.6</v>
+        <v>1334</v>
       </c>
       <c r="H89" s="4" t="n">
         <v/>
       </c>
       <c r="I89" s="4" t="n">
-        <v>206.9</v>
+        <v>109.5</v>
       </c>
       <c r="J89" s="4" t="n">
         <v/>
       </c>
       <c r="K89" s="4" t="n">
-        <v>376.9</v>
+        <v>146.8</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>0.51</v>
+        <v>0.823</v>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>James Qureshi; Emma Mueller; Amanda Qureshi; Ravi Qureshi; Jennifer Ueno</t>
+          <t>Hannah Zhang; Sophie Ueno; Laura Vega; Thomas Gupta</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -5140,55 +5156,51 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Tech</t>
+          <t>Glacier Tech</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
-        <v>50.5</v>
+        <v>368.6</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>96.2</v>
+        <v/>
       </c>
       <c r="I90" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>7.9</v>
+        <v/>
       </c>
       <c r="K90" s="4" t="n">
-        <v>12.8</v>
+        <v>154.7</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0.919</v>
+        <v>0.375</v>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>Emma Evans; Ahmed Schmidt</t>
+          <t>Laura Qureshi; Laura Williams; Ravi Lopez; Rachel Chen; Robert Brown</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -5200,17 +5212,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Dynamics</t>
+          <t>Vertex Media</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5220,31 +5232,31 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
-        <v>341.1</v>
+        <v>626.1</v>
       </c>
       <c r="H91" s="4" t="n">
         <v/>
       </c>
       <c r="I91" s="4" t="n">
-        <v>32.3</v>
+        <v>52.9</v>
       </c>
       <c r="J91" s="4" t="n">
         <v/>
       </c>
       <c r="K91" s="4" t="n">
-        <v>49.4</v>
+        <v>236.5</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>0.959</v>
+        <v>0.296</v>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>Matthew Chen; Robert Anderson; Wei Ueno</t>
+          <t>Emma Patel; Olivia Qureshi; Elena Brown; Jessica Ivanov; Jessica Vega</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -5256,7 +5268,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Vertex AG</t>
+          <t>Nimbus Foods</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5266,7 +5278,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -5276,35 +5288,35 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1986.1</v>
+        <v>1103.3</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>4202.8</v>
+        <v>1508.6</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>354.2</v>
+        <v>111.9</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>377.4</v>
+        <v>160.2</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>246.7</v>
+        <v>147.9</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.885</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>Olivia Hassan; Daniel Evans</t>
+          <t>Matthew Lopez; Sophie Lopez; Amanda Hassan; Emma Zhang; Priya Zhang</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -5314,41 +5326,139 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Fund VI Average</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="n">
-        <v>1104.4</v>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>2023.8</v>
-      </c>
-      <c r="I93" s="6" t="n">
-        <v>190.7</v>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>228.1</v>
-      </c>
-      <c r="K93" s="6" t="n">
-        <v>470.4</v>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Bloom Solutions</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>1680.3</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>5287.9</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>601.2</v>
+      </c>
+      <c r="K93" s="4" t="n">
+        <v>648.2</v>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>Thomas Gupta; Hannah Hassan; Daniel Qureshi</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>Fund VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Wavelength Systems</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>1715.3</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>2544.8</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>Sophie Xu; Robert Rossi; Sophie Gupta; Amanda Mueller; Andrew Rossi</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Fund VI</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Energy</t>
+          <t>Polaris Health</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5358,215 +5468,113 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="G95" s="4" t="n">
-        <v>725.7</v>
+        <v>1951.5</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>2428.1</v>
+        <v>1978.1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>69.8</v>
+        <v>181.1</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>150.8</v>
+        <v>232.8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>69</v>
+        <v>600.9</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>0.161</v>
+        <v>0.29</v>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>Amanda O'Brien; Christopher Mueller</t>
+          <t>Sarah Ivanov; Emma Ueno</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>Fund VII</t>
+          <t>Fund VI</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>Lumen Corp</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>1005.1</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>2071.4</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>299.8</v>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="M96" s="4" t="inlineStr">
-        <is>
-          <t>Priya Ivanov; Ravi Davis</t>
-        </is>
-      </c>
-      <c r="N96" s="4" t="inlineStr">
-        <is>
-          <t>Fund VII</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Xenith Solutions</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>2023-12-22</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>348.3</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>968.7</v>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="J97" s="4" t="n">
-        <v>132.4</v>
-      </c>
-      <c r="K97" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="M97" s="4" t="inlineStr">
-        <is>
-          <t>Emma Schmidt; Matthew Tanaka; Elena Johnson; Robert Kim; James Evans</t>
-        </is>
-      </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>Fund VII</t>
-        </is>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Fund VI Average</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>1023.9</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>1899</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>300.7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Zenith Capital</t>
+          <t>Echo Partners</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2023-01-08</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
-        <v>1923</v>
+        <v>828</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>3310.4</v>
+        <v/>
       </c>
       <c r="I98" s="4" t="n">
-        <v>386.1</v>
+        <v>110</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>720.1</v>
+        <v/>
       </c>
       <c r="K98" s="4" t="n">
-        <v>584.1</v>
+        <v>465.8</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.974</v>
+        <v>0.783</v>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>Christopher Williams; Daniel Kim; Ravi Yamamoto; Rachel Mueller</t>
+          <t>Thomas Kim; Olivia Anderson</t>
         </is>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -5578,17 +5586,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Stratus Foods</t>
+          <t>Drift Capital</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5598,35 +5606,35 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="G99" s="4" t="n">
-        <v>527.3</v>
+        <v>1957.8</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>840.5</v>
+        <v>1670.9</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>56.7</v>
+        <v>202.7</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>123.9</v>
+        <v>344</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>142.2</v>
+        <v>557</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>0.334</v>
+        <v>0.889</v>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>Andrew Tanaka; Emma Mueller; Laura Mueller</t>
+          <t>Daniel Kim; Christopher Brown; Sarah Tanaka</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -5638,51 +5646,55 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Echo Corp</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr"/>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
-        <v>646.1</v>
+        <v>1949.8</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v/>
+        <v>6301.3</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>410.9</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v/>
+        <v>601.9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>287.9</v>
+        <v>712.9</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.274</v>
+        <v>0.248</v>
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>Wei Vega; Jessica Vega; Sophie Brown; David Schmidt; Priya Qureshi</t>
+          <t>Hannah Zhang; James O'Brien; Yuki Fischer; Elena Schmidt</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -5694,17 +5706,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Meridian GmbH</t>
+          <t>Stratus Solutions</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5714,31 +5726,31 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
-        <v>975</v>
+        <v>1479.8</v>
       </c>
       <c r="H101" s="4" t="n">
         <v/>
       </c>
       <c r="I101" s="4" t="n">
-        <v>78.40000000000001</v>
+        <v>400</v>
       </c>
       <c r="J101" s="4" t="n">
         <v/>
       </c>
       <c r="K101" s="4" t="n">
-        <v>43.5</v>
+        <v>1068.7</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>0.388</v>
+        <v>0.376</v>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>Priya Xu; Rachel Ivanov; Andrew Mueller</t>
+          <t>Thomas Xu; Mark Patel; Emma O'Brien</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -5750,17 +5762,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Yields Pharma</t>
+          <t>Meridian Capital</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5770,31 +5782,31 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
-        <v>1198.7</v>
+        <v>929.3</v>
       </c>
       <c r="H102" s="4" t="n">
         <v/>
       </c>
       <c r="I102" s="4" t="n">
-        <v>165.1</v>
+        <v>78</v>
       </c>
       <c r="J102" s="4" t="n">
         <v/>
       </c>
       <c r="K102" s="4" t="n">
-        <v>373.5</v>
+        <v>135.7</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.271</v>
+        <v>0.819</v>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>Christopher Johnson; Christopher Ueno</t>
+          <t>Priya Yamamoto; David Ivanov; Wei Mueller; Rachel Ueno</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -5806,17 +5818,17 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Zenith Labs</t>
+          <t>Cobalt Labs</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5826,35 +5838,35 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1365.3</v>
+        <v>635.2</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>4428.9</v>
+        <v>624.5</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>323.2</v>
+        <v>87.3</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>334.5</v>
+        <v>133.4</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>621.1</v>
+        <v>289.5</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>0.273</v>
+        <v>0.984</v>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>Hannah Nakamura; Rachel Zhang; Christopher Rossi; Hannah Anderson; Rachel Rossi</t>
+          <t>Yuki Nakamura; Sarah Ueno; Yuki Chen; Sarah Hassan</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -5866,7 +5878,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Energy</t>
+          <t>Xenith Logistics</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -5876,7 +5888,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5886,31 +5898,31 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-03-11</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="4" t="n">
-        <v>1780.9</v>
+        <v>414.4</v>
       </c>
       <c r="H104" s="4" t="n">
         <v/>
       </c>
       <c r="I104" s="4" t="n">
-        <v>193.2</v>
+        <v>95.3</v>
       </c>
       <c r="J104" s="4" t="n">
         <v/>
       </c>
       <c r="K104" s="4" t="n">
-        <v>623.8</v>
+        <v>308.2</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.387</v>
+        <v>0.914</v>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>Amanda Anderson; Christopher Kim; Sophie Yamamoto; Laura Kim; Daniel Hassan</t>
+          <t>Ravi Kim; Wei Brown; Matthew Xu; Ahmed Vega</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -5922,51 +5934,55 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Vertex Dynamics</t>
+          <t>Vertex Partners</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
       <c r="G105" s="4" t="n">
-        <v>799.4</v>
+        <v>1713.1</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v/>
+        <v>1314.5</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>154.9</v>
+        <v>386.8</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v/>
+        <v>537.5</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>163.4</v>
+        <v>1353.5</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>0.999</v>
+        <v>0.854</v>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>Mark Johnson; Sophie Gupta; Sophie Brown; Michael Evans; Olivia Mueller</t>
+          <t>Olivia Evans; David Zhang</t>
         </is>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -5978,51 +5994,55 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Meridian Energy</t>
+          <t>Indigo Media</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
       <c r="G106" s="4" t="n">
-        <v>369.3</v>
+        <v>1803</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v/>
+        <v>4662.1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>50.6</v>
+        <v>326.3</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v/>
+        <v>680.7</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>216.8</v>
+        <v>686.4</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.157</v>
+        <v>0.994</v>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>Thomas Ueno; Daniel Zhang; Laura Vega; Sophie Tanaka; Jessica Johnson</t>
+          <t>Daniel Johnson; James Ivanov</t>
         </is>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -6034,17 +6054,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Indigo Industries</t>
+          <t>Beacon Partners</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6054,35 +6074,35 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-04-19</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>548.1</v>
+        <v>1200.5</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>945.2</v>
+        <v>1057.5</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>307.7</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>133.1</v>
+        <v>363.7</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>211.2</v>
+        <v>468.1</v>
       </c>
       <c r="L107" s="4" t="n">
-        <v>0.612</v>
+        <v>0.951</v>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>Sarah Mueller; Rachel Rossi; Sophie Nakamura; Wei Williams; Priya Chen</t>
+          <t>Mark Qureshi; Christopher Rossi; Thomas Chen</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -6094,12 +6114,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Gravity Group</t>
+          <t>Cobalt Health</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -6114,31 +6134,31 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="n">
-        <v>1886.5</v>
+        <v>250.9</v>
       </c>
       <c r="H108" s="4" t="n">
         <v/>
       </c>
       <c r="I108" s="4" t="n">
-        <v>464.2</v>
+        <v>23.2</v>
       </c>
       <c r="J108" s="4" t="n">
         <v/>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1829.8</v>
+        <v>58.3</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.464</v>
+        <v>0.268</v>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>James Schmidt; Thomas Yamamoto; Ahmed Evans; David Williams</t>
+          <t>Elena Anderson; Michael Lopez; Jennifer Patel; James Johnson; Mark Chen</t>
         </is>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -6150,55 +6170,51 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Vertex Capital</t>
+          <t>Junction Health</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
-        <v>1501.4</v>
+        <v>703.5</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>3675.8</v>
+        <v/>
       </c>
       <c r="I109" s="4" t="n">
-        <v>227.8</v>
+        <v>178.4</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>363.2</v>
+        <v/>
       </c>
       <c r="K109" s="4" t="n">
-        <v>744.4</v>
+        <v>758.3</v>
       </c>
       <c r="L109" s="4" t="n">
-        <v>0.575</v>
+        <v>0.556</v>
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>Sarah Patel; Emma Anderson</t>
+          <t>Laura Schmidt; Olivia O'Brien; Christopher Ueno; Matthew Brown; James Gupta</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -6208,311 +6224,311 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>Echo Systems</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>Zurich, CH</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>691.1</v>
-      </c>
-      <c r="H110" s="4" t="n">
-        <v>1156.1</v>
-      </c>
-      <c r="I110" s="4" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="J110" s="4" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="K110" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="L110" s="4" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="M110" s="4" t="inlineStr">
-        <is>
-          <t>Christopher Fischer; Rachel Evans; Daniel Chen; Wei Anderson</t>
-        </is>
-      </c>
-      <c r="N110" s="4" t="inlineStr">
-        <is>
-          <t>Fund VII</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Lattice Logistics</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="n">
-        <v>1188.5</v>
-      </c>
-      <c r="H111" s="4" t="n">
-        <v>1070</v>
-      </c>
-      <c r="I111" s="4" t="n">
-        <v>182.7</v>
-      </c>
-      <c r="J111" s="4" t="n">
-        <v>375.4</v>
-      </c>
-      <c r="K111" s="4" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="L111" s="4" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="M111" s="4" t="inlineStr">
-        <is>
-          <t>Sarah Davis; Rachel Schmidt</t>
-        </is>
-      </c>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>Fund VII</t>
-        </is>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Fund VII Average</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>1155.4</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>2605.1</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>217.2</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="K110" s="6" t="n">
+        <v>571.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Yields Labs</t>
+          <t>Lattice Pharma</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
+          <t>2027-03-12</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
-        <v>1936.8</v>
+        <v>115.6</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>5961.7</v>
+        <v/>
       </c>
       <c r="I112" s="4" t="n">
-        <v>444</v>
+        <v>11.9</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>867.9</v>
+        <v/>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1533.6</v>
+        <v>47.6</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.508</v>
+        <v>0.747</v>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>Thomas Qureshi; Mark Gupta; Robert Davis; Olivia Evans; Jennifer Qureshi</t>
+          <t>Yuki Zhang; Yuki Schmidt; Emma Gupta; Mark Rossi; Christopher Rossi</t>
         </is>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>Fund VII</t>
+          <t>Fund VIII</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Zenith SA</t>
+          <t>Lattice Foods</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>2027-09-21</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>1796.1</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>6238.7</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="J113" s="4" t="n">
+        <v>458.9</v>
+      </c>
+      <c r="K113" s="4" t="n">
+        <v>441.3</v>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M113" s="4" t="inlineStr">
+        <is>
+          <t>Emma Kim; Rachel Johnson; Christopher Schmidt; Jessica Patel</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>Fund VIII</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Cipher Pharma</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>1032.5</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>836.4</v>
+      </c>
+      <c r="I114" s="4" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="J114" s="4" t="n">
+        <v>313.8</v>
+      </c>
+      <c r="K114" s="4" t="n">
+        <v>1259.5</v>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>James Zhang; Hannah Williams; Ravi Xu; Amanda Lopez; Christopher Davis</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Fund VIII</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Nova Networks</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>Unrealized</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="n">
-        <v>182.7</v>
-      </c>
-      <c r="H113" s="4" t="n">
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="n">
+        <v>850.7</v>
+      </c>
+      <c r="H115" s="4" t="n">
         <v/>
       </c>
-      <c r="I113" s="4" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="J113" s="4" t="n">
+      <c r="I115" s="4" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="J115" s="4" t="n">
         <v/>
       </c>
-      <c r="K113" s="4" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="L113" s="4" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="M113" s="4" t="inlineStr">
-        <is>
-          <t>Sarah Chen; Robert Schmidt; Elena Lopez; David Yamamoto</t>
-        </is>
-      </c>
-      <c r="N113" s="4" t="inlineStr">
-        <is>
-          <t>Fund VII</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Fund VII Average</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="n">
-        <v>1031.5</v>
-      </c>
-      <c r="H114" s="6" t="n">
-        <v>2441.5</v>
-      </c>
-      <c r="I114" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="J114" s="6" t="n">
-        <v>312.6</v>
-      </c>
-      <c r="K114" s="6" t="n">
-        <v>435.5</v>
+      <c r="K115" s="4" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="L115" s="4" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="M115" s="4" t="inlineStr">
+        <is>
+          <t>Laura Johnson; Sophie Zhang; Mark Hassan</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Fund VIII</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Yields Foods</t>
+          <t>Xenith Systems</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr"/>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
-        <v>1601.2</v>
+        <v>1059.6</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v/>
+        <v>1996.7</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>352.4</v>
+        <v>132.5</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v/>
+        <v>223</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>261.3</v>
+        <v>165.2</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.977</v>
+        <v>0.885</v>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>Thomas Evans; Michael Xu; Priya Ueno; Elena Mueller; David Williams</t>
+          <t>Daniel Ueno; James Mueller; Daniel Davis</t>
         </is>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -6524,17 +6540,17 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Krypton Foods</t>
+          <t>Cipher Tech</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -6544,31 +6560,31 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
-        <v>1273</v>
+        <v>937.9</v>
       </c>
       <c r="H117" s="4" t="n">
         <v/>
       </c>
       <c r="I117" s="4" t="n">
-        <v>269.2</v>
+        <v>102.6</v>
       </c>
       <c r="J117" s="4" t="n">
         <v/>
       </c>
       <c r="K117" s="4" t="n">
-        <v>317.5</v>
+        <v>64.7</v>
       </c>
       <c r="L117" s="4" t="n">
-        <v>0.899</v>
+        <v>0.318</v>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>Jessica Gupta; Emma Johnson; Laura Schmidt; Yuki Chen</t>
+          <t>Laura Chen; Ravi Mueller; Jennifer Evans; Mark Chen</t>
         </is>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -6580,51 +6596,55 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Xenith Partners</t>
+          <t>Fathom Corp</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr"/>
+          <t>2027-12-15</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
-        <v>251.1</v>
+        <v>1484.2</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v/>
+        <v>3276.9</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>53.3</v>
+        <v>270.3</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v/>
+        <v>220.2</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>139.7</v>
+        <v>1082.9</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Gupta; Hannah Johnson; Ravi Gupta</t>
+          <t>Jessica Qureshi; Elena Ueno</t>
         </is>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -6636,55 +6656,51 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Echo Dynamics</t>
+          <t>Umbra Industries</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
+          <t>2024-04-28</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
-        <v>1223.1</v>
+        <v>1351</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>2421.7</v>
+        <v/>
       </c>
       <c r="I119" s="4" t="n">
-        <v>244.4</v>
+        <v>224.5</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>318.1</v>
+        <v/>
       </c>
       <c r="K119" s="4" t="n">
-        <v>370.5</v>
+        <v>974.8</v>
       </c>
       <c r="L119" s="4" t="n">
-        <v>0.453</v>
+        <v>0.319</v>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>Robert Brown; Rachel Fischer; Andrew Williams</t>
+          <t>Ravi Zhang; Thomas Evans</t>
         </is>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -6696,17 +6712,17 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Echo Industries</t>
+          <t>Echo Materials</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -6716,31 +6732,31 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
-        <v>536.7</v>
+        <v>853.3</v>
       </c>
       <c r="H120" s="4" t="n">
         <v/>
       </c>
       <c r="I120" s="4" t="n">
-        <v>118.6</v>
+        <v>226.1</v>
       </c>
       <c r="J120" s="4" t="n">
         <v/>
       </c>
       <c r="K120" s="4" t="n">
-        <v>180.8</v>
+        <v>284.5</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.916</v>
+        <v>0.794</v>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>Amanda Gupta; Robert Hassan; Sophie Tanaka</t>
+          <t>Daniel Anderson; Mark Yamamoto; David Davis</t>
         </is>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -6752,17 +6768,17 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Kepler GmbH</t>
+          <t>Radial Dynamics</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -6772,31 +6788,31 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
-        <v>1450.2</v>
+        <v>386</v>
       </c>
       <c r="H121" s="4" t="n">
         <v/>
       </c>
       <c r="I121" s="4" t="n">
-        <v>306.9</v>
+        <v>100.1</v>
       </c>
       <c r="J121" s="4" t="n">
         <v/>
       </c>
       <c r="K121" s="4" t="n">
-        <v>239</v>
+        <v>177.5</v>
       </c>
       <c r="L121" s="4" t="n">
-        <v>0.419</v>
+        <v>0.533</v>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>Ravi Mueller; Sarah Nakamura; Priya Fischer; Sophie Qureshi</t>
+          <t>Amanda Hassan; Christopher Johnson; Amanda Kim; Hannah Ivanov</t>
         </is>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -6808,17 +6824,17 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Umbra Foods</t>
+          <t>Fathom Networks</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -6828,31 +6844,31 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
-        <v>546</v>
+        <v>80.8</v>
       </c>
       <c r="H122" s="4" t="n">
         <v/>
       </c>
       <c r="I122" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J122" s="4" t="n">
         <v/>
       </c>
       <c r="K122" s="4" t="n">
-        <v>246.4</v>
+        <v>25.8</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.207</v>
+        <v>0.999</v>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>Wei Ivanov; Matthew Kim</t>
+          <t>Robert Davis; Jessica Ivanov; Hannah Schmidt</t>
         </is>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -6864,51 +6880,55 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Cipher Industries</t>
+          <t>Beacon Dynamics</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
-        <v>106.5</v>
+        <v>1008.4</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v/>
+        <v>1639.1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>13.3</v>
+        <v>156.9</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v/>
+        <v>323.5</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>39.9</v>
+        <v>534.3</v>
       </c>
       <c r="L123" s="4" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.965</v>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>Priya Johnson; David Rossi; Rachel Tanaka; Mark Fischer; Laura Chen</t>
+          <t>David Evans; Sarah Patel; Yuki Lopez; James Tanaka</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -6920,51 +6940,55 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Gravity Corp</t>
+          <t>Forge Pharma</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
-        <v>1570.5</v>
+        <v>1484.8</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v/>
+        <v>3843.2</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>159.5</v>
+        <v>300.9</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v/>
+        <v>745.9</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>445.3</v>
+        <v>1011.3</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.276</v>
+        <v>0.252</v>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>Emma Davis; Thomas Qureshi; Andrew Gupta; Ahmed Evans; Robert Vega</t>
+          <t>Ravi Qureshi; Sarah Brown</t>
         </is>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -6976,17 +7000,17 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Gravity Labs</t>
+          <t>Orion Holdings</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -6996,31 +7020,31 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
-        <v>738.8</v>
+        <v>1371</v>
       </c>
       <c r="H125" s="4" t="n">
         <v/>
       </c>
       <c r="I125" s="4" t="n">
-        <v>120.6</v>
+        <v>371.1</v>
       </c>
       <c r="J125" s="4" t="n">
         <v/>
       </c>
       <c r="K125" s="4" t="n">
-        <v>333.2</v>
+        <v>1633.2</v>
       </c>
       <c r="L125" s="4" t="n">
-        <v>0.72</v>
+        <v>0.789</v>
       </c>
       <c r="M125" s="4" t="inlineStr">
         <is>
-          <t>Priya Tanaka; Christopher Tanaka; Matthew Ivanov; Andrew Nakamura; Christopher Chen</t>
+          <t>Matthew Fischer; Mark Ivanov; Sarah Vega</t>
         </is>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -7032,17 +7056,17 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Zenith Ltd</t>
+          <t>Nova Group</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -7052,31 +7076,31 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
-        <v>231.7</v>
+        <v>928.1</v>
       </c>
       <c r="H126" s="4" t="n">
         <v/>
       </c>
       <c r="I126" s="4" t="n">
-        <v>26.9</v>
+        <v>116.1</v>
       </c>
       <c r="J126" s="4" t="n">
         <v/>
       </c>
       <c r="K126" s="4" t="n">
-        <v>42.6</v>
+        <v>481.5</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>0.265</v>
+        <v>0.217</v>
       </c>
       <c r="M126" s="4" t="inlineStr">
         <is>
-          <t>Mark Qureshi; Daniel Johnson; Yuki Hassan; Ravi Vega; Sarah Ueno</t>
+          <t>Laura Anderson; Sarah Xu; Ravi Fischer; Ahmed Evans</t>
         </is>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -7088,17 +7112,17 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Lattice AG</t>
+          <t>Polaris Dynamics</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -7108,31 +7132,31 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
-        <v>58</v>
+        <v>1067.8</v>
       </c>
       <c r="H127" s="4" t="n">
         <v/>
       </c>
       <c r="I127" s="4" t="n">
-        <v>4.8</v>
+        <v>154.3</v>
       </c>
       <c r="J127" s="4" t="n">
         <v/>
       </c>
       <c r="K127" s="4" t="n">
-        <v>9.1</v>
+        <v>353.7</v>
       </c>
       <c r="L127" s="4" t="n">
-        <v>0.912</v>
+        <v>0.544</v>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>Robert Qureshi; Sophie Kim; Jennifer Ueno; Michael Mueller; Sarah Chen</t>
+          <t>Matthew Fischer; Wei Johnson; Thomas O'Brien</t>
         </is>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -7144,17 +7168,17 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Stratus Corp</t>
+          <t>Umbra Dynamics</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -7164,31 +7188,31 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
-        <v>646.8</v>
+        <v>1976.7</v>
       </c>
       <c r="H128" s="4" t="n">
         <v/>
       </c>
       <c r="I128" s="4" t="n">
-        <v>127.5</v>
+        <v>207.1</v>
       </c>
       <c r="J128" s="4" t="n">
         <v/>
       </c>
       <c r="K128" s="4" t="n">
-        <v>465.8</v>
+        <v>398.4</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>0.961</v>
+        <v>0.827</v>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>Laura Hassan; James Patel</t>
+          <t>Mark Xu; Wei Zhang; Michael Qureshi; Amanda Tanaka</t>
         </is>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -7198,25 +7222,85 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Beacon Logistics</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Munich, DE</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1113.9</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>1582.4</v>
+      </c>
+      <c r="I129" s="4" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>635.3</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>311.3</v>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>Robert Schmidt; Elena Ivanov</t>
+        </is>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Fund VIII</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>Fund VIII Average</t>
         </is>
       </c>
-      <c r="G129" s="6" t="n">
-        <v>787.2</v>
-      </c>
-      <c r="H129" s="6" t="n">
-        <v>2421.7</v>
-      </c>
-      <c r="I129" s="6" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="J129" s="6" t="n">
-        <v>318.1</v>
-      </c>
-      <c r="K129" s="6" t="n">
-        <v>237.8</v>
+      <c r="G130" s="6" t="n">
+        <v>1049.9</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>2773.3</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>417.2</v>
+      </c>
+      <c r="K130" s="6" t="n">
+        <v>522.1</v>
       </c>
     </row>
   </sheetData>
